--- a/docs/design-docs/15_エラーコード一覧.xlsx
+++ b/docs/design-docs/15_エラーコード一覧.xlsx
@@ -10,7 +10,419 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>エラーコード一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-ERR-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>業務エラー</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>メッセージ(ja)</t>
+  </si>
+  <si>
+    <t>発生条件</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-001</t>
+  </si>
+  <si>
+    <t>重複</t>
+  </si>
+  <si>
+    <t>同じ設備codeが既に存在</t>
+  </si>
+  <si>
+    <t>設備code重複</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-002</t>
+  </si>
+  <si>
+    <t>同じloginIDが既に使用</t>
+  </si>
+  <si>
+    <t>loginID重複</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-003</t>
+  </si>
+  <si>
+    <t>指定範囲に既存休日</t>
+  </si>
+  <si>
+    <t>休日重複</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-006</t>
+  </si>
+  <si>
+    <t>状態不正</t>
+  </si>
+  <si>
+    <t>廃止済設備は親設備不可</t>
+  </si>
+  <si>
+    <t>廃止設備→親指定</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-007</t>
+  </si>
+  <si>
+    <t>承認済点検結果は修正不可</t>
+  </si>
+  <si>
+    <t>承認済data修正</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-009</t>
+  </si>
+  <si>
+    <t>在庫不足</t>
+  </si>
+  <si>
+    <t>使用量が現在庫を超過</t>
+  </si>
+  <si>
+    <t>在庫超え使用</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-010</t>
+  </si>
+  <si>
+    <t>期限切れ</t>
+  </si>
+  <si>
+    <t>認定有効期限が切れています</t>
+  </si>
+  <si>
+    <t>期限切れ資格</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-012</t>
+  </si>
+  <si>
+    <t>操作不正</t>
+  </si>
+  <si>
+    <t>全明細完了していない</t>
+  </si>
+  <si>
+    <t>未了明細あり</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-013</t>
+  </si>
+  <si>
+    <t>差戻理由未入力</t>
+  </si>
+  <si>
+    <t>理由未入力</t>
+  </si>
+  <si>
+    <t>ERR-BIZ-014</t>
+  </si>
+  <si>
+    <t>過去日</t>
+  </si>
+  <si>
+    <t>過去日は指定不可</t>
+  </si>
+  <si>
+    <t>過去日指定</t>
+  </si>
+  <si>
+    <t>バリデーションエラー</t>
+  </si>
+  <si>
+    <t>ERR-VAL-001</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>{0}は必須</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>ERR-VAL-002</t>
+  </si>
+  <si>
+    <t>最大長</t>
+  </si>
+  <si>
+    <t>{0}は{1}文字以内</t>
+  </si>
+  <si>
+    <t>maxlength</t>
+  </si>
+  <si>
+    <t>ERR-VAL-003</t>
+  </si>
+  <si>
+    <t>数値範囲</t>
+  </si>
+  <si>
+    <t>{0}は{1}〜{2}</t>
+  </si>
+  <si>
+    <t>intRange</t>
+  </si>
+  <si>
+    <t>ERR-VAL-004</t>
+  </si>
+  <si>
+    <t>形式</t>
+  </si>
+  <si>
+    <t>{0}は日付形式</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>ERR-VAL-005</t>
+  </si>
+  <si>
+    <t>フリガナはkatakana</t>
+  </si>
+  <si>
+    <t>mask</t>
+  </si>
+  <si>
+    <t>ERR-VAL-006</t>
+  </si>
+  <si>
+    <t>一致</t>
+  </si>
+  <si>
+    <t>password不一致</t>
+  </si>
+  <si>
+    <t>confirm</t>
+  </si>
+  <si>
+    <t>ERR-VAL-007</t>
+  </si>
+  <si>
+    <t>最小長</t>
+  </si>
+  <si>
+    <t>password8文字以上</t>
+  </si>
+  <si>
+    <t>minlength</t>
+  </si>
+  <si>
+    <t>ERR-VAL-008</t>
+  </si>
+  <si>
+    <t>条件付必須</t>
+  </si>
+  <si>
+    <t>×判定時 実測値必須</t>
+  </si>
+  <si>
+    <t>conditional</t>
+  </si>
+  <si>
+    <t>ERR-VAL-009</t>
+  </si>
+  <si>
+    <t>×/△判定時 所見必須</t>
+  </si>
+  <si>
+    <t>ERR-VAL-010</t>
+  </si>
+  <si>
+    <t>推定原因必須</t>
+  </si>
+  <si>
+    <t>ERR-VAL-011</t>
+  </si>
+  <si>
+    <t>対応内容必須</t>
+  </si>
+  <si>
+    <t>ERR-VAL-014</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>file size{0}MB以下</t>
+  </si>
+  <si>
+    <t>file size</t>
+  </si>
+  <si>
+    <t>ERR-VAL-015</t>
+  </si>
+  <si>
+    <t>file形式{0}のみ</t>
+  </si>
+  <si>
+    <t>file ext</t>
+  </si>
+  <si>
+    <t>ERR-VAL-018</t>
+  </si>
+  <si>
+    <t>行数</t>
+  </si>
+  <si>
+    <t>明細1行以上必要</t>
+  </si>
+  <si>
+    <t>min rows</t>
+  </si>
+  <si>
+    <t>ERR-VAL-019</t>
+  </si>
+  <si>
+    <t>明細最大50行</t>
+  </si>
+  <si>
+    <t>max rows</t>
+  </si>
+  <si>
+    <t>システムエラー</t>
+  </si>
+  <si>
+    <t>HTTP</t>
+  </si>
+  <si>
+    <t>ERR-SYS-001</t>
+  </si>
+  <si>
+    <t>DB接続</t>
+  </si>
+  <si>
+    <t>システムエラー発生 管理者連絡</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>ERR-SYS-002</t>
+  </si>
+  <si>
+    <t>fileIO</t>
+  </si>
+  <si>
+    <t>file読書失敗</t>
+  </si>
+  <si>
+    <t>ERR-SYS-003</t>
+  </si>
+  <si>
+    <t>認証</t>
+  </si>
+  <si>
+    <t>login失敗 ID/password確認</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>ERR-SYS-004</t>
+  </si>
+  <si>
+    <t>session</t>
+  </si>
+  <si>
+    <t>session切れ 再login</t>
+  </si>
+  <si>
+    <t>ERR-SYS-005</t>
+  </si>
+  <si>
+    <t>権限</t>
+  </si>
+  <si>
+    <t>操作権限なし</t>
+  </si>
+  <si>
+    <t>ERR-SYS-006</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>pageなし</t>
+  </si>
+  <si>
+    <t>ERR-SYS-007</t>
+  </si>
+  <si>
+    <t>予期せぬエラー</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
